--- a/output/pdf_financials_xlsx/ASTN.P.xlsx
+++ b/output/pdf_financials_xlsx/ASTN.P.xlsx
@@ -957,25 +957,25 @@
         <v>-0.010141</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.120074</v>
+        <v>-0.120074</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.067923</v>
+        <v>-0.067923</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.072731</v>
+        <v>-0.072731</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.060143</v>
+        <v>-0.060143</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.035255</v>
+        <v>-0.035255</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.019671</v>
+        <v>-0.019671</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.034043</v>
+        <v>-0.034043</v>
       </c>
     </row>
     <row r="17">
@@ -1133,25 +1133,25 @@
         <v>-0.010141</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.120074</v>
+        <v>-0.120074</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.067923</v>
+        <v>-0.067923</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.072731</v>
+        <v>-0.072731</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.060143</v>
+        <v>-0.060143</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.035255</v>
+        <v>-0.035255</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.019671</v>
+        <v>-0.019671</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.034043</v>
+        <v>-0.034043</v>
       </c>
     </row>
     <row r="21">
@@ -1239,25 +1239,25 @@
         <v>-0.010141</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.120074</v>
+        <v>-0.120074</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.067923</v>
+        <v>-0.067923</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.072731</v>
+        <v>-0.072731</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.060143</v>
+        <v>-0.060143</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.035255</v>
+        <v>-0.035255</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.019671</v>
+        <v>-0.019671</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.034043</v>
+        <v>-0.034043</v>
       </c>
     </row>
     <row r="24">
@@ -1353,16 +1353,16 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1.000617</v>
+        <v>-1.000617</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>3.39615</v>
+        <v>-3.39615</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.63655</v>
+        <v>-3.63655</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3.00715</v>
+        <v>-3.00715</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1395,25 +1395,25 @@
         <v>-0.010141</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.120074</v>
+        <v>-0.120074</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.067923</v>
+        <v>-0.067923</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.072731</v>
+        <v>-0.072731</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.060143</v>
+        <v>-0.060143</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.035255</v>
+        <v>-0.035255</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.019671</v>
+        <v>-0.019671</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.034043</v>
+        <v>-0.034043</v>
       </c>
     </row>
     <row r="28">
@@ -1467,25 +1467,25 @@
         <v>-0.010141</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.120074</v>
+        <v>-0.120074</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.067923</v>
+        <v>-0.067923</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.072731</v>
+        <v>-0.072731</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.060143</v>
+        <v>-0.060143</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.035255</v>
+        <v>-0.035255</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.019671</v>
+        <v>-0.019671</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.034043</v>
+        <v>-0.034043</v>
       </c>
     </row>
     <row r="30">
@@ -1555,25 +1555,25 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -8231,25 +8231,25 @@
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.120074</v>
+        <v>-0.120074</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.067923</v>
+        <v>-0.067923</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>0.072731</v>
+        <v>-0.072731</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>0.060143</v>
+        <v>-0.060143</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.035255</v>
+        <v>-0.035255</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0.019671</v>
+        <v>-0.019671</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.034043</v>
+        <v>-0.034043</v>
       </c>
     </row>
     <row r="51">

--- a/output/pdf_financials_xlsx/ASTN.P.xlsx
+++ b/output/pdf_financials_xlsx/ASTN.P.xlsx
@@ -813,25 +813,25 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000957</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003762</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001939</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000677</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001659</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002862</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0009879999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1395,25 +1395,25 @@
         <v>-0.010141</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.120074</v>
+        <v>-0.119117</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.067923</v>
+        <v>-0.064161</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.072731</v>
+        <v>-0.07079199999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.060143</v>
+        <v>-0.059466</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.035255</v>
+        <v>-0.033596</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.019671</v>
+        <v>-0.016809</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.034043</v>
+        <v>-0.033055</v>
       </c>
     </row>
     <row r="28">
@@ -1467,25 +1467,25 @@
         <v>-0.010141</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.120074</v>
+        <v>-0.119117</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.067923</v>
+        <v>-0.064161</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.072731</v>
+        <v>-0.07079199999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.060143</v>
+        <v>-0.059466</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.035255</v>
+        <v>-0.033596</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.019671</v>
+        <v>-0.016809</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.034043</v>
+        <v>-0.033055</v>
       </c>
     </row>
     <row r="30">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
